--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -503,7 +503,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|ServiceRequest)
 </t>
   </si>
   <si>
@@ -525,7 +525,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationadministration|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationdispense|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationstatement|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation)
 </t>
   </si>
   <si>
@@ -750,7 +750,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -815,7 +815,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T06:51:53+00:00</t>
+    <t>2026-02-05T08:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-medicationstatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
